--- a/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_4_b_lab_enu_kad.xlsx
+++ b/ONCHO/Entomological survey Survey/Nigeria/2025/enugu-kaduna/ng_oncho_2505_4_b_lab_enu_kad.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bonhe\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\ONCHO\Entomological survey Survey\Nigeria\2025\enugu-kaduna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D28D65A-8858-4E45-9C72-B33AA8E6A009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9DC1522-0F32-462A-9844-EF53BB40ACEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="228">
   <si>
     <t>type</t>
   </si>
@@ -410,21 +410,6 @@
     <t>testing_lap</t>
   </si>
   <si>
-    <t>pools_pos_det_ebo</t>
-  </si>
-  <si>
-    <t>pools_neg_det_ebo</t>
-  </si>
-  <si>
-    <t>pools_l_100_det_ebo</t>
-  </si>
-  <si>
-    <t>ng_oncho_2505_4_b_lab_enu_kad</t>
-  </si>
-  <si>
-    <t>(Enugu Kaduna) 4. Blackfly Lab App</t>
-  </si>
-  <si>
     <t>ENUGU</t>
   </si>
   <si>
@@ -717,6 +702,24 @@
   </si>
   <si>
     <t>KAD_JEM_M_001</t>
+  </si>
+  <si>
+    <t>ng_oncho_2505_4_b_lab_enu_kad_v2</t>
+  </si>
+  <si>
+    <t>(Enugu Kaduna) 4. Blackfly Lab App V2</t>
+  </si>
+  <si>
+    <t>pools_pos_det_ebo_2</t>
+  </si>
+  <si>
+    <t>pools_neg_det_ebo_2</t>
+  </si>
+  <si>
+    <t>pools_l_100_det_ebo_2</t>
+  </si>
+  <si>
+    <t>ENU_ENE_M_096</t>
   </si>
 </sst>
 </file>
@@ -1691,7 +1694,7 @@
         <v>44</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="C9" s="20" t="s">
         <v>49</v>
@@ -1849,7 +1852,7 @@
         <v>44</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>125</v>
+        <v>225</v>
       </c>
       <c r="C16" s="20" t="s">
         <v>50</v>
@@ -2007,7 +2010,7 @@
         <v>44</v>
       </c>
       <c r="B23" s="19" t="s">
-        <v>126</v>
+        <v>226</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>54</v>
@@ -2374,7 +2377,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.125" customWidth="1"/>
@@ -2501,10 +2504,10 @@
         <v>68</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2512,10 +2515,10 @@
         <v>68</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2529,13 +2532,13 @@
         <v>70</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C17" s="23" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D17" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2543,13 +2546,13 @@
         <v>70</v>
       </c>
       <c r="B18" s="23" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C18" s="23" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D18" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2557,13 +2560,13 @@
         <v>70</v>
       </c>
       <c r="B19" s="23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C19" s="23" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D19" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2571,13 +2574,13 @@
         <v>70</v>
       </c>
       <c r="B20" s="23" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C20" s="23" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D20" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2585,13 +2588,13 @@
         <v>70</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2599,13 +2602,13 @@
         <v>70</v>
       </c>
       <c r="B22" s="23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C22" s="23" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D22" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2613,13 +2616,13 @@
         <v>70</v>
       </c>
       <c r="B23" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="C23" s="23" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D23" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2627,13 +2630,13 @@
         <v>70</v>
       </c>
       <c r="B24" s="23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C24" s="23" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D24" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2641,13 +2644,13 @@
         <v>70</v>
       </c>
       <c r="B25" s="23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="C25" s="23" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D25" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2655,13 +2658,13 @@
         <v>70</v>
       </c>
       <c r="B26" s="23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C26" s="23" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D26" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2669,13 +2672,13 @@
         <v>70</v>
       </c>
       <c r="B27" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C27" s="23" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D27" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -2683,13 +2686,13 @@
         <v>70</v>
       </c>
       <c r="B28" s="23" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C28" s="23" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D28" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2697,13 +2700,13 @@
         <v>70</v>
       </c>
       <c r="B29" s="23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C29" s="23" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D29" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,13 +2714,13 @@
         <v>70</v>
       </c>
       <c r="B30" s="23" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C30" s="23" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D30" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2725,13 +2728,13 @@
         <v>70</v>
       </c>
       <c r="B31" s="23" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C31" s="23" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D31" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2739,13 +2742,13 @@
         <v>70</v>
       </c>
       <c r="B32" s="23" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C32" s="23" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D32" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2753,13 +2756,13 @@
         <v>70</v>
       </c>
       <c r="B33" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C33" s="23" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D33" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2767,13 +2770,13 @@
         <v>70</v>
       </c>
       <c r="B34" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C34" s="23" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D34" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2781,13 +2784,13 @@
         <v>70</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C35" s="23" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D35" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2795,13 +2798,13 @@
         <v>70</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C36" s="23" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D36" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2809,13 +2812,13 @@
         <v>70</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C37" s="23" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D37" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2823,13 +2826,13 @@
         <v>70</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D38" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2837,13 +2840,13 @@
         <v>70</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C39" s="23" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D39" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2851,13 +2854,13 @@
         <v>70</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C40" s="23" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D40" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2865,13 +2868,13 @@
         <v>70</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C41" s="23" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D41" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2879,13 +2882,13 @@
         <v>70</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C42" s="23" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D42" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2893,13 +2896,13 @@
         <v>70</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D43" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2907,13 +2910,13 @@
         <v>70</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D44" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2921,13 +2924,13 @@
         <v>70</v>
       </c>
       <c r="B45" s="23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D45" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2935,13 +2938,13 @@
         <v>70</v>
       </c>
       <c r="B46" s="23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D46" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2949,13 +2952,13 @@
         <v>70</v>
       </c>
       <c r="B47" s="23" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C47" s="23" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D47" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2963,13 +2966,13 @@
         <v>70</v>
       </c>
       <c r="B48" s="23" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="C48" s="23" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D48" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2977,13 +2980,13 @@
         <v>70</v>
       </c>
       <c r="B49" s="23" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C49" s="23" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D49" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2991,13 +2994,13 @@
         <v>70</v>
       </c>
       <c r="B50" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C50" s="23" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D50" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -3005,13 +3008,13 @@
         <v>70</v>
       </c>
       <c r="B51" s="23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="C51" s="23" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D51" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -3019,13 +3022,13 @@
         <v>70</v>
       </c>
       <c r="B52" s="23" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -3033,13 +3036,13 @@
         <v>70</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C53" s="23" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D53" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -3047,13 +3050,13 @@
         <v>70</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C54" s="23" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D54" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3061,13 +3064,13 @@
         <v>70</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C55" s="23" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3075,13 +3078,13 @@
         <v>70</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C56" s="23" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3089,13 +3092,13 @@
         <v>70</v>
       </c>
       <c r="B57" s="23" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C57" s="23" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3103,13 +3106,13 @@
         <v>70</v>
       </c>
       <c r="B58" s="23" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C58" s="23" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -3117,13 +3120,13 @@
         <v>70</v>
       </c>
       <c r="B59" s="23" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C59" s="23" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D59" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -3131,13 +3134,13 @@
         <v>70</v>
       </c>
       <c r="B60" s="23" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C60" s="23" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D60" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -3145,13 +3148,13 @@
         <v>70</v>
       </c>
       <c r="B61" s="23" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C61" s="23" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D61" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -3159,13 +3162,13 @@
         <v>70</v>
       </c>
       <c r="B62" s="23" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C62" s="23" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D62" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -3173,13 +3176,13 @@
         <v>70</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C63" s="23" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D63" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -3187,13 +3190,13 @@
         <v>70</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C64" s="23" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D64" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -3201,13 +3204,13 @@
         <v>70</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C65" s="23" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="D65" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
@@ -3215,13 +3218,13 @@
         <v>70</v>
       </c>
       <c r="B66" s="23" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C66" s="23" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D66" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -3229,13 +3232,13 @@
         <v>70</v>
       </c>
       <c r="B67" s="23" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C67" s="23" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D67" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -3243,13 +3246,13 @@
         <v>70</v>
       </c>
       <c r="B68" s="23" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C68" s="23" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="D68" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -3257,13 +3260,13 @@
         <v>70</v>
       </c>
       <c r="B69" s="23" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C69" s="23" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D69" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -3271,13 +3274,13 @@
         <v>70</v>
       </c>
       <c r="B70" s="23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C70" s="23" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D70" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -3285,13 +3288,13 @@
         <v>70</v>
       </c>
       <c r="B71" s="23" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C71" s="23" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D71" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -3299,13 +3302,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="23" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C72" s="23" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D72" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
@@ -3313,13 +3316,13 @@
         <v>70</v>
       </c>
       <c r="B73" s="23" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C73" s="23" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="D73" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
@@ -3327,13 +3330,13 @@
         <v>70</v>
       </c>
       <c r="B74" s="23" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C74" s="23" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="D74" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
@@ -3341,13 +3344,13 @@
         <v>70</v>
       </c>
       <c r="B75" s="23" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C75" s="23" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D75" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
@@ -3355,13 +3358,13 @@
         <v>70</v>
       </c>
       <c r="B76" s="23" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C76" s="23" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D76" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
@@ -3369,13 +3372,13 @@
         <v>70</v>
       </c>
       <c r="B77" s="23" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C77" s="23" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="D77" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
@@ -3383,13 +3386,13 @@
         <v>70</v>
       </c>
       <c r="B78" s="23" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C78" s="23" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D78" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -3397,13 +3400,13 @@
         <v>70</v>
       </c>
       <c r="B79" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C79" s="23" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="D79" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
@@ -3411,13 +3414,13 @@
         <v>70</v>
       </c>
       <c r="B80" s="23" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C80" s="23" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="D80" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -3425,13 +3428,13 @@
         <v>70</v>
       </c>
       <c r="B81" s="23" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C81" s="23" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D81" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -3439,13 +3442,13 @@
         <v>70</v>
       </c>
       <c r="B82" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C82" s="23" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D82" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -3453,13 +3456,13 @@
         <v>70</v>
       </c>
       <c r="B83" s="23" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C83" s="23" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="D83" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -3467,13 +3470,13 @@
         <v>70</v>
       </c>
       <c r="B84" s="23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C84" s="23" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D84" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -3481,13 +3484,13 @@
         <v>70</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="D85" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
@@ -3495,13 +3498,13 @@
         <v>70</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="D86" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
@@ -3509,13 +3512,13 @@
         <v>70</v>
       </c>
       <c r="B87" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="D87" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
@@ -3523,13 +3526,13 @@
         <v>70</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D88" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
@@ -3537,13 +3540,13 @@
         <v>70</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="D89" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
@@ -3551,13 +3554,13 @@
         <v>70</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D90" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -3565,13 +3568,13 @@
         <v>70</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D91" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -3579,13 +3582,13 @@
         <v>70</v>
       </c>
       <c r="B92" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D92" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -3593,13 +3596,13 @@
         <v>70</v>
       </c>
       <c r="B93" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D93" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
@@ -3607,13 +3610,13 @@
         <v>70</v>
       </c>
       <c r="B94" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D94" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
@@ -3621,13 +3624,13 @@
         <v>70</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D95" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
@@ -3635,13 +3638,13 @@
         <v>70</v>
       </c>
       <c r="B96" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D96" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -3649,13 +3652,13 @@
         <v>70</v>
       </c>
       <c r="B97" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C97" s="16" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -3663,13 +3666,13 @@
         <v>70</v>
       </c>
       <c r="B98" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="C98" s="16" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D98" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
@@ -3677,13 +3680,13 @@
         <v>70</v>
       </c>
       <c r="B99" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C99" s="16" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D99" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -3691,13 +3694,13 @@
         <v>70</v>
       </c>
       <c r="B100" s="16" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="C100" s="16" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D100" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
@@ -3705,13 +3708,13 @@
         <v>70</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D101" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -3719,13 +3722,13 @@
         <v>70</v>
       </c>
       <c r="B102" s="16" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C102" s="16" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D102" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
@@ -3733,13 +3736,13 @@
         <v>70</v>
       </c>
       <c r="B103" s="16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C103" s="16" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D103" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -3747,13 +3750,13 @@
         <v>70</v>
       </c>
       <c r="B104" s="16" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C104" s="16" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D104" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
@@ -3761,13 +3764,13 @@
         <v>70</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="C105" s="16" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D105" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
@@ -3775,13 +3778,13 @@
         <v>70</v>
       </c>
       <c r="B106" s="16" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C106" s="16" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D106" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -3789,13 +3792,13 @@
         <v>70</v>
       </c>
       <c r="B107" s="16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C107" s="16" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D107" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
@@ -3803,13 +3806,13 @@
         <v>70</v>
       </c>
       <c r="B108" s="16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="C108" s="16" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D108" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
@@ -3817,13 +3820,13 @@
         <v>70</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C109" s="16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D109" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
@@ -3831,13 +3834,13 @@
         <v>70</v>
       </c>
       <c r="B110" s="16" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C110" s="16" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D110" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
@@ -3845,13 +3848,13 @@
         <v>70</v>
       </c>
       <c r="B111" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C111" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D111" s="23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
@@ -3859,61 +3862,72 @@
         <v>70</v>
       </c>
       <c r="B112" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C112" s="16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D112" s="23" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D113" s="16"/>
-    </row>
-    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>70</v>
+      </c>
+      <c r="B113" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="C113" s="16" t="s">
+        <v>221</v>
+      </c>
+      <c r="D113" s="23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D114" s="16"/>
     </row>
-    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D115" s="16"/>
     </row>
-    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D116" s="16"/>
     </row>
-    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D117" s="16"/>
     </row>
-    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D118" s="16"/>
     </row>
-    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D119" s="16"/>
     </row>
-    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D120" s="16"/>
     </row>
-    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D121" s="16"/>
     </row>
-    <row r="122" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D122" s="16"/>
     </row>
-    <row r="123" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D123" s="16"/>
     </row>
-    <row r="124" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D124" s="16"/>
     </row>
-    <row r="125" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D125" s="16"/>
     </row>
-    <row r="126" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D126" s="16"/>
     </row>
-    <row r="127" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D127" s="16"/>
     </row>
-    <row r="128" spans="4:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="D128" s="16"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
@@ -3929,10 +3943,7 @@
       <c r="D132" s="16"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="17"/>
-      <c r="B133" s="23"/>
-      <c r="C133" s="23"/>
-      <c r="D133" s="23"/>
+      <c r="D133" s="16"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="17"/>
@@ -4553,6 +4564,9 @@
       <c r="D236" s="23"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A237" s="17"/>
+      <c r="B237" s="23"/>
+      <c r="C237" s="23"/>
       <c r="D237" s="23"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.25">
@@ -4567,24 +4581,27 @@
     <row r="241" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D241" s="23"/>
     </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D242" s="23"/>
+    </row>
   </sheetData>
+  <conditionalFormatting sqref="B17:B60">
+    <cfRule type="duplicateValues" dxfId="7" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="11"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B61:B73">
-    <cfRule type="duplicateValues" dxfId="7" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B74:B80">
-    <cfRule type="duplicateValues" dxfId="5" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C131:C176">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B17:B60">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="11"/>
+  <conditionalFormatting sqref="C132:C177">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -4615,10 +4632,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>128</v>
+        <v>223</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>127</v>
+        <v>222</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>19</v>
